--- a/history/nbv_history_DPEN_True.xlsx
+++ b/history/nbv_history_DPEN_True.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,13 +477,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2218.555592105263</v>
+        <v>1826.409789210432</v>
       </c>
       <c r="C3" t="n">
         <v>1.842744691558805</v>
       </c>
       <c r="D3" t="n">
-        <v>2218.555592105263</v>
+        <v>1826.409789210432</v>
       </c>
       <c r="E3" t="n">
         <v>1.842744691558805</v>
@@ -494,16 +494,50 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1988.536691272253</v>
+        <v>1685.242731887402</v>
       </c>
       <c r="C4" t="n">
         <v>4.514671187971725</v>
       </c>
       <c r="D4" t="n">
-        <v>4207.092283377517</v>
+        <v>3511.652521097834</v>
       </c>
       <c r="E4" t="n">
         <v>6.35741587953053</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97.14625850340136</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2.394898624579488</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3608.798779601236</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8.752314504110018</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>24.46640926640926</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.676764562891517</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3633.265188867645</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11.42907906700153</v>
       </c>
     </row>
   </sheetData>
